--- a/base_datas/mediana_nacional_detalhamento.xlsx
+++ b/base_datas/mediana_nacional_detalhamento.xlsx
@@ -593,13 +593,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>602.067527038123</v>
+        <v>602.3307916122346</v>
       </c>
       <c r="B2">
-        <v>108.3755793163891</v>
+        <v>108.4884501715428</v>
       </c>
       <c r="C2">
-        <v>6555.033092422434</v>
+        <v>6572.102231683037</v>
       </c>
       <c r="D2">
         <v>278.9823633760378</v>
@@ -608,34 +608,34 @@
         <v>541.7074282875725</v>
       </c>
       <c r="F2">
-        <v>35.2467117938037</v>
+        <v>35.19666666666667</v>
       </c>
       <c r="G2">
-        <v>2.000860977511061</v>
+        <v>1.981087844083813</v>
       </c>
       <c r="H2">
-        <v>209.4127089220832</v>
+        <v>209.6784642760852</v>
       </c>
       <c r="I2">
-        <v>62.13437882607131</v>
+        <v>62.28473090364453</v>
       </c>
       <c r="J2">
-        <v>6.091853575454464E-15</v>
+        <v>6.056815319287601E-15</v>
       </c>
       <c r="K2">
-        <v>3923.566145125477</v>
+        <v>3938.222127711708</v>
       </c>
       <c r="L2">
-        <v>1571.134506420546</v>
+        <v>1572.083360846247</v>
       </c>
       <c r="M2">
-        <v>998.3218496933579</v>
+        <v>999.1768856122117</v>
       </c>
       <c r="N2">
-        <v>182.1828301886792</v>
+        <v>182.1583330433269</v>
       </c>
       <c r="O2">
-        <v>18.33140997429052</v>
+        <v>18.45875438234687</v>
       </c>
       <c r="P2">
         <v>1.123054409836313</v>
@@ -644,19 +644,19 @@
         <v>4.634388781527179</v>
       </c>
       <c r="R2">
-        <v>31.12356269113198</v>
+        <v>31.04079607187534</v>
       </c>
       <c r="S2">
-        <v>52.32102995323394</v>
+        <v>52.26856366928183</v>
       </c>
       <c r="T2">
-        <v>50.04128178797767</v>
+        <v>50.27717091295117</v>
       </c>
       <c r="U2">
-        <v>169.5171110808788</v>
+        <v>169.8457578496484</v>
       </c>
       <c r="V2">
-        <v>196.9430305151993</v>
+        <v>196.8933716123105</v>
       </c>
       <c r="W2">
         <v>4203.961932344067</v>
@@ -665,70 +665,70 @@
         <v>660.8749918098674</v>
       </c>
       <c r="Y2">
-        <v>1.841140626710973E-14</v>
+        <v>1.836929081210417E-14</v>
       </c>
       <c r="Z2">
-        <v>15.00266346963904</v>
+        <v>14.98380995389805</v>
       </c>
       <c r="AA2">
-        <v>19.55350760103819</v>
+        <v>19.52751675545626</v>
       </c>
       <c r="AB2">
-        <v>6.220213409441415E-17</v>
+        <v>6.629936592600439E-17</v>
       </c>
       <c r="AC2">
-        <v>1.302940984675579</v>
+        <v>1.236525951668872</v>
       </c>
       <c r="AD2">
         <v>2.153846647417388</v>
       </c>
       <c r="AE2">
-        <v>27.35073428749222</v>
+        <v>27.7285557212076</v>
       </c>
       <c r="AF2">
         <v>0.2418682872429404</v>
       </c>
       <c r="AG2">
-        <v>2338.467914243425</v>
+        <v>2342.606215855069</v>
       </c>
       <c r="AH2">
         <v>467.5037520550409</v>
       </c>
       <c r="AI2">
-        <v>53.69797424372972</v>
+        <v>54.06339944808555</v>
       </c>
       <c r="AJ2">
-        <v>610.9664631896319</v>
+        <v>611.5843394753956</v>
       </c>
       <c r="AK2">
-        <v>106.2441010154062</v>
+        <v>106.3653178969148</v>
       </c>
       <c r="AL2">
-        <v>72.42662979121221</v>
+        <v>72.52946052511018</v>
       </c>
       <c r="AM2">
-        <v>30.84181133108004</v>
+        <v>30.87287975077881</v>
       </c>
       <c r="AN2">
-        <v>49.20950274137245</v>
+        <v>49.44106820207809</v>
       </c>
       <c r="AO2">
-        <v>1093.670813906006</v>
+        <v>1093.600537497098</v>
       </c>
       <c r="AP2">
-        <v>145.8691759230892</v>
+        <v>145.5125418994413</v>
       </c>
       <c r="AQ2">
-        <v>78.17589576547232</v>
+        <v>77.82353228583983</v>
       </c>
       <c r="AR2">
-        <v>10.9782873871676</v>
+        <v>10.97712843800822</v>
       </c>
       <c r="AS2">
-        <v>3.778966161138575</v>
+        <v>3.750735040630387</v>
       </c>
       <c r="AT2">
-        <v>101.2691655140618</v>
+        <v>101.4406697278608</v>
       </c>
       <c r="AU2">
         <v>1</v>

--- a/base_datas/mediana_nacional_detalhamento.xlsx
+++ b/base_datas/mediana_nacional_detalhamento.xlsx
@@ -593,49 +593,49 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>602.067527038123</v>
+        <v>602.1946040578026</v>
       </c>
       <c r="B2">
-        <v>108.3755793163891</v>
+        <v>108.464650548584</v>
       </c>
       <c r="C2">
-        <v>6555.033092422434</v>
+        <v>6572.056932999803</v>
       </c>
       <c r="D2">
-        <v>278.9823633760378</v>
+        <v>278.9219806846598</v>
       </c>
       <c r="E2">
-        <v>541.7074282875725</v>
+        <v>541.661208142794</v>
       </c>
       <c r="F2">
-        <v>35.2467117938037</v>
+        <v>35.19514076295185</v>
       </c>
       <c r="G2">
-        <v>2.000860977511061</v>
+        <v>1.976051536255104</v>
       </c>
       <c r="H2">
-        <v>209.4127089220832</v>
+        <v>209.6615152797742</v>
       </c>
       <c r="I2">
-        <v>62.13437882607131</v>
+        <v>62.26162030920135</v>
       </c>
       <c r="J2">
-        <v>6.091853575454464E-15</v>
+        <v>6.056815319287601E-15</v>
       </c>
       <c r="K2">
-        <v>3923.566145125477</v>
+        <v>3938.160160889279</v>
       </c>
       <c r="L2">
-        <v>1571.134506420546</v>
+        <v>1572.057907107935</v>
       </c>
       <c r="M2">
-        <v>998.3218496933579</v>
+        <v>999.1080273373428</v>
       </c>
       <c r="N2">
-        <v>182.1828301886792</v>
+        <v>182.1705816160031</v>
       </c>
       <c r="O2">
-        <v>18.33140997429052</v>
+        <v>18.45256945355475</v>
       </c>
       <c r="P2">
         <v>1.123054409836313</v>
@@ -644,19 +644,19 @@
         <v>4.634388781527179</v>
       </c>
       <c r="R2">
-        <v>31.12356269113198</v>
+        <v>31.03533796245959</v>
       </c>
       <c r="S2">
-        <v>52.32102995323394</v>
+        <v>52.23612026347266</v>
       </c>
       <c r="T2">
-        <v>50.04128178797767</v>
+        <v>50.25364062209135</v>
       </c>
       <c r="U2">
-        <v>169.5171110808788</v>
+        <v>169.8448160208401</v>
       </c>
       <c r="V2">
-        <v>196.9430305151993</v>
+        <v>196.8726803493695</v>
       </c>
       <c r="W2">
         <v>4203.961932344067</v>
@@ -665,70 +665,70 @@
         <v>660.8749918098674</v>
       </c>
       <c r="Y2">
-        <v>1.841140626710973E-14</v>
+        <v>1.835624752868729E-14</v>
       </c>
       <c r="Z2">
-        <v>15.00266346963904</v>
+        <v>14.96938223303524</v>
       </c>
       <c r="AA2">
-        <v>19.55350760103819</v>
+        <v>19.52684175217312</v>
       </c>
       <c r="AB2">
-        <v>6.220213409441415E-17</v>
+        <v>6.629936592600439E-17</v>
       </c>
       <c r="AC2">
-        <v>1.302940984675579</v>
+        <v>1.240288446610985</v>
       </c>
       <c r="AD2">
         <v>2.153846647417388</v>
       </c>
       <c r="AE2">
-        <v>27.35073428749222</v>
+        <v>27.7285557212076</v>
       </c>
       <c r="AF2">
         <v>0.2418682872429404</v>
       </c>
       <c r="AG2">
-        <v>2338.467914243425</v>
+        <v>2342.535689636163</v>
       </c>
       <c r="AH2">
         <v>467.5037520550409</v>
       </c>
       <c r="AI2">
-        <v>53.69797424372972</v>
+        <v>54.0587772905827</v>
       </c>
       <c r="AJ2">
-        <v>610.9664631896319</v>
+        <v>611.5681818073456</v>
       </c>
       <c r="AK2">
-        <v>106.2441010154062</v>
+        <v>106.3464554903486</v>
       </c>
       <c r="AL2">
-        <v>72.42662979121221</v>
+        <v>72.52946052511018</v>
       </c>
       <c r="AM2">
-        <v>30.84181133108004</v>
+        <v>30.86789603069548</v>
       </c>
       <c r="AN2">
-        <v>49.20950274137245</v>
+        <v>49.45450849645037</v>
       </c>
       <c r="AO2">
-        <v>1093.670813906006</v>
+        <v>1093.294726351581</v>
       </c>
       <c r="AP2">
-        <v>145.8691759230892</v>
+        <v>145.4702123043462</v>
       </c>
       <c r="AQ2">
-        <v>78.17589576547232</v>
+        <v>77.78843640020111</v>
       </c>
       <c r="AR2">
-        <v>10.9782873871676</v>
+        <v>10.97712843800822</v>
       </c>
       <c r="AS2">
-        <v>3.778966161138575</v>
+        <v>3.750735040630387</v>
       </c>
       <c r="AT2">
-        <v>101.2691655140618</v>
+        <v>101.4333552540814</v>
       </c>
       <c r="AU2">
         <v>1</v>
